--- a/graficos/BERT_mejores_dominio.xlsx
+++ b/graficos/BERT_mejores_dominio.xlsx
@@ -49,34 +49,34 @@
     <t>comisión_lim</t>
   </si>
   <si>
-    <t>denuncia</t>
-  </si>
-  <si>
-    <t>comisión_lim_denuncia_K41_0.01</t>
-  </si>
-  <si>
-    <t>denuncia_dictamen</t>
-  </si>
-  <si>
-    <t>comisión_lim_denuncia_dictamen_K45_0.01</t>
-  </si>
-  <si>
-    <t>denuncia_bert</t>
-  </si>
-  <si>
-    <t>comisión_lim_denuncia_bert_K32_0.01</t>
-  </si>
-  <si>
-    <t>denuncia_dictamen_bert</t>
-  </si>
-  <si>
-    <t>comisión_lim_denuncia_dictamen_bert_K40_0.01</t>
+    <t>antecedentes</t>
+  </si>
+  <si>
+    <t>comisión_lim_antecedentes_K41_0.01</t>
+  </si>
+  <si>
+    <t>antecedentes_dictamen</t>
+  </si>
+  <si>
+    <t>comisión_lim_antecedentes_dictamen_K45_0.01</t>
+  </si>
+  <si>
+    <t>antecedentes_bert</t>
+  </si>
+  <si>
+    <t>comisión_lim_antecedentes_bert_K32_0.01</t>
+  </si>
+  <si>
+    <t>antecedentes_dictamen_bert</t>
+  </si>
+  <si>
+    <t>comisión_lim_antecedentes_dictamen_bert_K40_0.01</t>
   </si>
   <si>
     <t>todos</t>
   </si>
   <si>
-    <t>todos_denuncia_bert_K12_0.01</t>
+    <t>todos_antecedentes_bert_K12_0.01</t>
   </si>
   <si>
     <t>contenido_bert</t>
@@ -88,25 +88,25 @@
     <t>orps_lim</t>
   </si>
   <si>
-    <t>orps_lim_denuncia_K35_0.01</t>
+    <t>orps_lim_antecedentes_K35_0.01</t>
   </si>
   <si>
     <t>comisión</t>
   </si>
   <si>
-    <t>comisión_denuncia_K22_0.01</t>
+    <t>comisión_antecedentes_K22_0.01</t>
   </si>
   <si>
     <t>orps</t>
   </si>
   <si>
-    <t>orps_denuncia_bert_K24_0.01</t>
-  </si>
-  <si>
-    <t>orps_lim_denuncia_bert_K35_0.01</t>
-  </si>
-  <si>
-    <t>todos_denuncia_K17_0.01</t>
+    <t>orps_antecedentes_bert_K24_0.01</t>
+  </si>
+  <si>
+    <t>orps_lim_antecedentes_bert_K35_0.01</t>
+  </si>
+  <si>
+    <t>todos_antecedentes_K17_0.01</t>
   </si>
   <si>
     <t>contenido</t>
@@ -130,19 +130,19 @@
     <t>orps_lim_contenido_K35_0.01</t>
   </si>
   <si>
-    <t>comisión_denuncia_bert_K15_0.01</t>
-  </si>
-  <si>
-    <t>orps_lim_denuncia_dictamen_bert_K21_0.01</t>
+    <t>orps_antecedentes_K15_0.01</t>
   </si>
   <si>
     <t>dictamen</t>
   </si>
   <si>
-    <t>orps_lim_dictamen_K36_0.01</t>
-  </si>
-  <si>
-    <t>comisión_denuncia_dictamen_K15_0.01</t>
+    <t>comisión_dictamen_K31_0.01</t>
+  </si>
+  <si>
+    <t>todos_antecedentes_dictamen_bert_K25_0.01</t>
+  </si>
+  <si>
+    <t>orps_dictamen_K24_0.01</t>
   </si>
 </sst>
 </file>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C18" s="2">
         <v>15</v>
@@ -1078,62 +1078,62 @@
         <v>38</v>
       </c>
       <c r="F18" s="3">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="G18" s="3">
-        <v>-1.072831596669709</v>
+        <v>-0.9432633946232171</v>
       </c>
       <c r="H18" s="2">
         <v>3</v>
       </c>
       <c r="I18" s="2">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="J18" s="3">
-        <v>0.03614457831325301</v>
+        <v>0.0375</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="C19" s="2">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D19" s="3">
         <v>0.01</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F19" s="3">
-        <v>0.2428571428571429</v>
+        <v>0.2516129032258064</v>
       </c>
       <c r="G19" s="3">
-        <v>-0.6507753263095919</v>
+        <v>-0.6418524881443924</v>
       </c>
       <c r="H19" s="2">
         <v>3</v>
       </c>
       <c r="I19" s="2">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="J19" s="3">
-        <v>0.03571428571428571</v>
+        <v>0.02631578947368421</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="C20" s="2">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D20" s="3">
         <v>0.01</v>
@@ -1142,30 +1142,30 @@
         <v>41</v>
       </c>
       <c r="F20" s="3">
-        <v>0.2305555555555556</v>
+        <v>0.236</v>
       </c>
       <c r="G20" s="3">
-        <v>-1.01264076812605</v>
+        <v>-1.097786417658492</v>
       </c>
       <c r="H20" s="2">
         <v>3</v>
       </c>
       <c r="I20" s="2">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="J20" s="3">
-        <v>0.0234375</v>
+        <v>0.03191489361702127</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C21" s="2">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D21" s="3">
         <v>0.01</v>
@@ -1174,19 +1174,19 @@
         <v>42</v>
       </c>
       <c r="F21" s="3">
-        <v>0.1533333333333333</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="G21" s="3">
-        <v>-0.5022998724955899</v>
+        <v>-0.5456087326647211</v>
       </c>
       <c r="H21" s="2">
         <v>3</v>
       </c>
       <c r="I21" s="2">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="J21" s="3">
-        <v>0.0625</v>
+        <v>0.03896103896103896</v>
       </c>
     </row>
   </sheetData>
